--- a/cv/cv.xlsx
+++ b/cv/cv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian/Dropbox/git-repos/cris_blog/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1547FADF-3A5E-8647-B66B-423B13F6CD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9771161-3076-1D43-BE2E-2658F14DDB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="680" windowWidth="27660" windowHeight="16460" activeTab="4" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
+    <workbookView xWindow="1120" yWindow="680" windowWidth="27660" windowHeight="16460" activeTab="5" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
   </bookViews>
   <sheets>
     <sheet name="employment" sheetId="5" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="104">
   <si>
     <t>degree</t>
   </si>
@@ -118,9 +118,6 @@
     <t>BSc. Sports and Exercise Science</t>
   </si>
   <si>
-    <t>My PhD thesis focused on the factors that hinder replicability and reproducibility of research in sports and exercise science</t>
-  </si>
-  <si>
     <t>My master thesis focused on the effect of two training protocols on maxymal oxygen uptake in highly-trained cyclists</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>Funding to develop an R package designed to assist master's students and supervisors in performing automatic checks to prevent statistical errors and enforce best research practices</t>
   </si>
   <si>
-    <t>Supervisor of a Master's thesis</t>
-  </si>
-  <si>
     <t>event</t>
   </si>
   <si>
@@ -202,9 +196,6 @@
     <t>Denmark</t>
   </si>
   <si>
-    <t xml:space="preserve">Workshop on Papercheck </t>
-  </si>
-  <si>
     <t>Open Research Summer School at King's College London</t>
   </si>
   <si>
@@ -250,36 +241,21 @@
     <t>Presented the findings from one of my PhD projects where we examined publication bias and average statistical power in sports and exercise science research</t>
   </si>
   <si>
-    <t xml:space="preserve">Gave a presentation about the tool Papercheck and then led a workshop on how to use it, including practical examples. The workshop materials are available here:  https://osf.io/r8fbd/ </t>
-  </si>
-  <si>
-    <t>Gave a talk about the benefits of preregistration and Registered Reports when conducting confirmatory studies. The slides are available at https://osf.io/tveh8/</t>
-  </si>
-  <si>
     <t>Conducted a workshop on the use of the 1080 Sprint resistance device to measure power–velocity profiles and estimate drag in swimmers.</t>
   </si>
   <si>
     <t>Co-supervised four students creating a tool to extract sample sizes from published studies</t>
   </si>
   <si>
-    <t>Co-supervised the creation of a tool to detect the incorrect use use of standard error of measurement instead of the standard deviation when computing effect sizes in meta-analyses</t>
-  </si>
-  <si>
     <t>Taught R Markdown for reproducible reporting and data simulation for statistical analysis</t>
   </si>
   <si>
-    <t>Co-supervised a student who conducted a meta-analysis examining the impact of school sanitation on students' academic performance</t>
-  </si>
-  <si>
     <t xml:space="preserve">Taught anatomy </t>
   </si>
   <si>
     <t>2021-2025</t>
   </si>
   <si>
-    <t>Contributing to the development of Papercheck, an R package that helps researchers identify and prevent poor research practices before publication and facilitates data extraction from published articles</t>
-  </si>
-  <si>
     <t>Together with my supervisor Pr. Raúl Arellano, I contributed to race analysis and the evaluation of swimmers' dry-land performance profiles. Additionally, I assessed propulsive force using the 30-second tethered swimming test with a load cell force measurement system.</t>
   </si>
   <si>
@@ -301,18 +277,9 @@
     <t>Lecturer of Behaveoral Research Methods 2</t>
   </si>
   <si>
-    <t>Teaching assistant of  of Behaveoral Research Methods 3</t>
-  </si>
-  <si>
     <t>Assisting students during tutorial sessions with conducting their assignments</t>
   </si>
   <si>
-    <t>Discussed whether research published in sports and exercise science journals complies with the Declaration of Helsinki, particularly in light of recent projects highlighting replication and reproducibility issues that contribute to research waste. The slides are available here: https://osf.io/bzp4s/files</t>
-  </si>
-  <si>
-    <t>2024-Presentation</t>
-  </si>
-  <si>
     <t>Dutch Research Council</t>
   </si>
   <si>
@@ -325,16 +292,67 @@
     <t>Lecturer of Metascience</t>
   </si>
   <si>
-    <t xml:space="preserve"> Teaching multiple regression, power analysis, and equivalence testing.  Teaching materials can be found at https://cristianmesquida.github.io/multiple_regression/</t>
-  </si>
-  <si>
     <t>Teaching Introduction to Meta-analysis as part of the Metascience course. Teaching materials can be found at https://github.com/cristianmesquida/introduction_to_meta-analysis</t>
   </si>
   <si>
-    <t>Supervisor of Mester End Project</t>
-  </si>
-  <si>
-    <t>Co-supervised a student who used automated search extraction (Metacheck) to extract hypotheses from academic articles and attempted to classify them using large language models</t>
+    <t>2024-Present</t>
+  </si>
+  <si>
+    <t>Lecturer of Behaveoral Research Methods 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Teaching philosophy of science, power analysis, and equivalence testing.  Teaching materials can be found at https://cristianmesquida.github.io/multiple_regression/</t>
+  </si>
+  <si>
+    <t>My PhD thesis focused on the factors that hinder replicability and reproducibility of research in sports and exercise science. You can find my thesis at: https://research.tue.nl/en/publications/an-investigation-into-the-barriers-to-replicability-and-reproduci/</t>
+  </si>
+  <si>
+    <t>Teaching assistant of Behaveoral Research Methods 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Teaching multiple regression and power analysis. Teaching materials can be found at https://cristianmesquida.github.io/multiple_regression/ and </t>
+  </si>
+  <si>
+    <t>Supervisor of Master End Project</t>
+  </si>
+  <si>
+    <t>Co-supervised a meta-analysis project examining the impact of school sanitation on students' academic performance</t>
+  </si>
+  <si>
+    <t>Co-supervised a project using automated search extraction to extract and attempted hypotheses using large language models</t>
+  </si>
+  <si>
+    <t>Co-supervised the development of a tool to identify incorrect use of the standard error of measurement instead of the standard deviation in effect size calculations for meta-analyses</t>
+  </si>
+  <si>
+    <t>Workshop on Metacheck</t>
+  </si>
+  <si>
+    <t>Contributing to the development of Metacheck, an R package that helps researchers identify and prevent poor research practices before publication and facilitates data extraction from published articles</t>
+  </si>
+  <si>
+    <t>Transparency, Technology and AI in Peer Review</t>
+  </si>
+  <si>
+    <t>Talk slides: https://cristianmesquida.github.io/technology_tue_conference_talk/#/title-slide</t>
+  </si>
+  <si>
+    <t>Talk slides: https://osf.io/bzp4s/files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop Materials:  https://osf.io/r8fbd/ </t>
+  </si>
+  <si>
+    <t>Talk slides: https://osf.io/tveh8/</t>
+  </si>
+  <si>
+    <t>ONH Metascience Symposium</t>
+  </si>
+  <si>
+    <t>Oslo Nye Høyskole</t>
+  </si>
+  <si>
+    <t>Talk slides: https://cristianmesquida.github.io/metascience_symposium_oslo/#/title-slide</t>
   </si>
 </sst>
 </file>
@@ -764,7 +782,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
@@ -784,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -792,7 +810,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
@@ -801,7 +819,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -832,18 +850,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -852,7 +870,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -869,7 +887,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -886,7 +904,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -903,7 +921,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +941,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -932,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -940,53 +958,53 @@
     </row>
     <row r="2" spans="1:5" s="10" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2" s="10">
         <v>2018</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="10" customFormat="1" ht="76" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B3" s="10">
         <v>2017</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>60</v>
-      </c>
       <c r="D4" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531F101D-2B48-9F46-A53F-FA67ACC31D52}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.33203125" style="7" customWidth="1"/>
@@ -1013,7 +1031,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -1030,89 +1048,106 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>86</v>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2024</v>
+        <v>45</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>30</v>
+      <c r="A5" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3">
         <v>2024</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>48</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3">
         <v>2021</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1139,7 +1174,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -1148,72 +1183,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3">
         <v>2025</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3">
         <v>2024</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3">
         <v>2023</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A465BE91-A970-8F4B-854C-C3F13E65FCA4}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" style="4" customWidth="1"/>
@@ -1235,7 +1270,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1244,150 +1279,184 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="13" customFormat="1" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="5">
-        <v>2025</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="5">
-        <v>2025</v>
+    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2026</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="13" customFormat="1" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5">
         <v>2025</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B5" s="5">
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="E10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2019</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="5">
-        <v>2019</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C16" s="9"/>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1420,22 +1489,22 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="3">
         <v>2026</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>92</v>
+      <c r="C2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>2024</v>
@@ -1444,7 +1513,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/cv/cv.xlsx
+++ b/cv/cv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian/Dropbox/git-repos/cris_blog/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9771161-3076-1D43-BE2E-2658F14DDB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934D250E-5865-044B-BB01-55671F1B06A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="680" windowWidth="27660" windowHeight="16460" activeTab="5" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
+    <workbookView xWindow="1120" yWindow="680" windowWidth="27660" windowHeight="16460" activeTab="6" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
   </bookViews>
   <sheets>
     <sheet name="employment" sheetId="5" r:id="rId1"/>
@@ -118,15 +118,6 @@
     <t>BSc. Sports and Exercise Science</t>
   </si>
   <si>
-    <t>My master thesis focused on the effect of two training protocols on maxymal oxygen uptake in highly-trained cyclists</t>
-  </si>
-  <si>
-    <t>My master thesis focused on the performance determinants of swimming sprint performance</t>
-  </si>
-  <si>
-    <t>My bachelor end project focused on developing a training programe to reduce the injury risk of hamstrings in football players</t>
-  </si>
-  <si>
     <t>Supervisor of Bachelor End Project</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t>IE&amp;IS ESA Education Innovation Grant</t>
   </si>
   <si>
-    <t>Funding to develop an R package designed to assist master's students and supervisors in performing automatic checks to prevent statistical errors and enforce best research practices</t>
-  </si>
-  <si>
     <t>event</t>
   </si>
   <si>
@@ -208,9 +196,6 @@
     <t>Research internship (unpaid)</t>
   </si>
   <si>
-    <t>Together with my supervisor Pr. Bent Rønnestad and my colleague Arthur Bossi, I investigated the effects of two high-intensity interval training (HIIT) protocols on maximal oxygen uptake (VO₂max) in highly trained cyclists. The study involved detailed physiological assessments, including lactate threshold testing, VO₂max measurements, and cycling economy evaluations.</t>
-  </si>
-  <si>
     <t>2015-2016</t>
   </si>
   <si>
@@ -232,18 +217,6 @@
     <t>Technological University of Dublin</t>
   </si>
   <si>
-    <t>Conducted a workshop on the physiological determinants of endurance performance and team sports and conducted a lactate-threshold test to estimate training zones based on blood lactate concentrations</t>
-  </si>
-  <si>
-    <t>Presented the findings from one of my PhD projects where we examined the reporting practices and reproducibility of a priori power analyses in sports and exercise science research</t>
-  </si>
-  <si>
-    <t>Presented the findings from one of my PhD projects where we examined publication bias and average statistical power in sports and exercise science research</t>
-  </si>
-  <si>
-    <t>Conducted a workshop on the use of the 1080 Sprint resistance device to measure power–velocity profiles and estimate drag in swimmers.</t>
-  </si>
-  <si>
     <t>Co-supervised four students creating a tool to extract sample sizes from published studies</t>
   </si>
   <si>
@@ -256,15 +229,6 @@
     <t>2021-2025</t>
   </si>
   <si>
-    <t>Together with my supervisor Pr. Raúl Arellano, I contributed to race analysis and the evaluation of swimmers' dry-land performance profiles. Additionally, I assessed propulsive force using the 30-second tethered swimming test with a load cell force measurement system.</t>
-  </si>
-  <si>
-    <t>Together with Pr. Bjørn Harald, I investigated the use of the 1080 Sprint resistance device in swimming to measure power–velocity profiles and estimate drag characteristics in swimmers.</t>
-  </si>
-  <si>
-    <t>My PhD thesis examined the factors hindering replicability and reproducibility  in sports and exercise science</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -277,42 +241,24 @@
     <t>Lecturer of Behaveoral Research Methods 2</t>
   </si>
   <si>
-    <t>Assisting students during tutorial sessions with conducting their assignments</t>
-  </si>
-  <si>
     <t>Dutch Research Council</t>
   </si>
   <si>
     <t>Replication studies</t>
   </si>
   <si>
-    <t>Assess the reproducibility of power analyses in large-scale replication projects. See project details at https://doi.org/10.61686/FSWVF35053</t>
-  </si>
-  <si>
     <t>Lecturer of Metascience</t>
   </si>
   <si>
-    <t>Teaching Introduction to Meta-analysis as part of the Metascience course. Teaching materials can be found at https://github.com/cristianmesquida/introduction_to_meta-analysis</t>
-  </si>
-  <si>
     <t>2024-Present</t>
   </si>
   <si>
     <t>Lecturer of Behaveoral Research Methods 3</t>
   </si>
   <si>
-    <t xml:space="preserve"> Teaching philosophy of science, power analysis, and equivalence testing.  Teaching materials can be found at https://cristianmesquida.github.io/multiple_regression/</t>
-  </si>
-  <si>
-    <t>My PhD thesis focused on the factors that hinder replicability and reproducibility of research in sports and exercise science. You can find my thesis at: https://research.tue.nl/en/publications/an-investigation-into-the-barriers-to-replicability-and-reproduci/</t>
-  </si>
-  <si>
     <t>Teaching assistant of Behaveoral Research Methods 3</t>
   </si>
   <si>
-    <t xml:space="preserve"> Teaching multiple regression and power analysis. Teaching materials can be found at https://cristianmesquida.github.io/multiple_regression/ and </t>
-  </si>
-  <si>
     <t>Supervisor of Master End Project</t>
   </si>
   <si>
@@ -328,38 +274,115 @@
     <t>Workshop on Metacheck</t>
   </si>
   <si>
-    <t>Contributing to the development of Metacheck, an R package that helps researchers identify and prevent poor research practices before publication and facilitates data extraction from published articles</t>
-  </si>
-  <si>
     <t>Transparency, Technology and AI in Peer Review</t>
   </si>
   <si>
-    <t>Talk slides: https://cristianmesquida.github.io/technology_tue_conference_talk/#/title-slide</t>
-  </si>
-  <si>
-    <t>Talk slides: https://osf.io/bzp4s/files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop Materials:  https://osf.io/r8fbd/ </t>
-  </si>
-  <si>
-    <t>Talk slides: https://osf.io/tveh8/</t>
-  </si>
-  <si>
     <t>ONH Metascience Symposium</t>
   </si>
   <si>
     <t>Oslo Nye Høyskole</t>
   </si>
   <si>
-    <t>Talk slides: https://cristianmesquida.github.io/metascience_symposium_oslo/#/title-slide</t>
+    <t>Presented findings on publication bias and statistical power in sports and exercise science.</t>
+  </si>
+  <si>
+    <t>Conducted a workshop on the physiological determinants of endurance and team-sport performance, including lactate-threshold testing.</t>
+  </si>
+  <si>
+    <t>Conducted a workshop on using the 1080 Sprint to assess swimmers' power–velocity profiles and drag</t>
+  </si>
+  <si>
+    <r>
+      <t>Presented findings on the reporting and reproducibility of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a priori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> power analyses in sports and exercise science.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Taught p-values and Bayes factors, power analysis, and equivalence testing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Taught multiple regression and power analysis.</t>
+  </si>
+  <si>
+    <t>Taught introduction to meta-analysis</t>
+  </si>
+  <si>
+    <t>Assisted students during tutorial sessions with course assignments</t>
+  </si>
+  <si>
+    <t>Investigated the effects of two HIIT protocols on VO₂max in highly trained cyclists using physiological assessments, including lactate threshold, VO₂max, and cycling economy testing.</t>
+  </si>
+  <si>
+    <t>Contributed to race analysis and the assessment of swimmers' dry-land performance profiles and propulsive force.</t>
+  </si>
+  <si>
+    <t>Investigated the use of the 1080 Sprint resistance device in swimming to measure power–velocity profiles and estimate drag characteristics in swimmers.</t>
+  </si>
+  <si>
+    <t>Funding to develop an R package designed to assist master's students and supervisors in performing automatic checks to enforce best research practices.</t>
+  </si>
+  <si>
+    <t>Assess the reproducibility of power analyses in large-scale replication projects. (Project details at https://doi.org/10.61686/FSWVF35053).</t>
+  </si>
+  <si>
+    <t>Presented findings on the quality of power analyses for sample size justification in sports and exercise science.</t>
+  </si>
+  <si>
+    <t>Presented Metacheck, an automated tool for assessing research transparency.</t>
+  </si>
+  <si>
+    <t>Gave a talk on research waste in sports and exercise science.</t>
+  </si>
+  <si>
+    <t>Delivered a workshop on Metacheck, including a presentation and hands-on session.</t>
+  </si>
+  <si>
+    <t>Gave a talk on the benefits of preregistration and Registered Reports in hypothesis-testing research.</t>
+  </si>
+  <si>
+    <t>My master thesis focused on the performance determinants of swimming sprint performance.</t>
+  </si>
+  <si>
+    <t>My master thesis focused on the effect of two training protocols on maxymal oxygen uptake in highly-trained cyclists.</t>
+  </si>
+  <si>
+    <t>My PhD thesis focused on the factors that hinder replicability and reproducibility of research in sports and exercise science.</t>
+  </si>
+  <si>
+    <t>My bachelor end project focused on developing a training programe to reduce the injury risk of hamstrings in football players.</t>
+  </si>
+  <si>
+    <t>Contributed to the development and validation of Metacheck, an R package for improving research quality and extracting data from published articles.</t>
+  </si>
+  <si>
+    <t>My PhD thesis examined the factors hindering replicability and reproducibility  in sports and exercise science.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -387,6 +410,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -408,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -442,10 +473,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,7 +819,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
@@ -802,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -810,7 +847,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
@@ -819,7 +856,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -850,18 +887,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -870,7 +907,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -887,7 +924,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -904,7 +941,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -921,7 +958,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -936,12 +973,12 @@
   <cols>
     <col min="1" max="1" width="26.1640625" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="5" max="5" width="81.6640625" customWidth="1"/>
+    <col min="5" max="5" width="81.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -950,61 +987,61 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="10" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B2" s="10">
         <v>2018</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="10" customFormat="1" ht="76" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B3" s="10">
         <v>2017</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="10" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="10" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>71</v>
+        <v>53</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1068,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -1040,106 +1077,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>2024</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3">
         <v>2024</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3">
         <v>2021</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1174,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -1185,70 +1222,70 @@
     </row>
     <row r="2" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3">
         <v>2025</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3">
         <v>2024</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>2023</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1265,12 +1302,12 @@
     <col min="2" max="2" width="17.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="24.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="47.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="47.5" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1279,32 +1316,32 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
@@ -1313,66 +1350,66 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="13" customFormat="1" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="12" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B4" s="5">
         <v>2025</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>98</v>
+        <v>62</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5">
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>99</v>
+        <v>44</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B6" s="5">
         <v>2025</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>100</v>
+        <v>46</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5">
         <v>2025</v>
@@ -1381,32 +1418,32 @@
         <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>100</v>
+        <v>32</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5">
         <v>2024</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9" s="5">
         <v>2024</v>
@@ -1415,44 +1452,44 @@
         <v>6</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="E10" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B11" s="5">
         <v>2019</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.2">
@@ -1490,21 +1527,21 @@
     </row>
     <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3">
         <v>2026</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2024</v>
@@ -1513,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/cv/cv.xlsx
+++ b/cv/cv.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian/Dropbox/git-repos/cris_blog/cv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934D250E-5865-044B-BB01-55671F1B06A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2868EA-A8D2-3740-8813-5BBF0C03502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="680" windowWidth="27660" windowHeight="16460" activeTab="6" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
+    <workbookView xWindow="1080" yWindow="600" windowWidth="27660" windowHeight="16460" xr2:uid="{DA4E0661-7526-1B46-BFDD-FC359AB20183}"/>
   </bookViews>
   <sheets>
-    <sheet name="employment" sheetId="5" r:id="rId1"/>
-    <sheet name="education" sheetId="1" r:id="rId2"/>
-    <sheet name="research_experience" sheetId="8" r:id="rId3"/>
-    <sheet name="teaching" sheetId="3" r:id="rId4"/>
-    <sheet name="supervision" sheetId="9" r:id="rId5"/>
-    <sheet name="talks" sheetId="6" r:id="rId6"/>
-    <sheet name="grants" sheetId="4" r:id="rId7"/>
+    <sheet name="references" sheetId="10" r:id="rId1"/>
+    <sheet name="organization" sheetId="11" r:id="rId2"/>
+    <sheet name="employment" sheetId="5" r:id="rId3"/>
+    <sheet name="education" sheetId="1" r:id="rId4"/>
+    <sheet name="qualifications" sheetId="8" r:id="rId5"/>
+    <sheet name="teaching" sheetId="3" r:id="rId6"/>
+    <sheet name="supervision" sheetId="9" r:id="rId7"/>
+    <sheet name="talks" sheetId="6" r:id="rId8"/>
+    <sheet name="grants" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="108">
   <si>
     <t>degree</t>
   </si>
@@ -157,15 +159,9 @@
     <t>position</t>
   </si>
   <si>
-    <t>Inland Norway University of Applied Sciences</t>
-  </si>
-  <si>
     <t>Norway</t>
   </si>
   <si>
-    <t>Norwegian School of Sports Science</t>
-  </si>
-  <si>
     <t>The Netherlands</t>
   </si>
   <si>
@@ -193,18 +189,6 @@
     <t>Danish Reproducibility Network meetup</t>
   </si>
   <si>
-    <t>Research internship (unpaid)</t>
-  </si>
-  <si>
-    <t>2015-2016</t>
-  </si>
-  <si>
-    <t>Universiry of Granada</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
@@ -217,15 +201,6 @@
     <t>Technological University of Dublin</t>
   </si>
   <si>
-    <t>Co-supervised four students creating a tool to extract sample sizes from published studies</t>
-  </si>
-  <si>
-    <t>Taught R Markdown for reproducible reporting and data simulation for statistical analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taught anatomy </t>
-  </si>
-  <si>
     <t>2021-2025</t>
   </si>
   <si>
@@ -253,22 +228,7 @@
     <t>2024-Present</t>
   </si>
   <si>
-    <t>Lecturer of Behaveoral Research Methods 3</t>
-  </si>
-  <si>
-    <t>Teaching assistant of Behaveoral Research Methods 3</t>
-  </si>
-  <si>
     <t>Supervisor of Master End Project</t>
-  </si>
-  <si>
-    <t>Co-supervised a meta-analysis project examining the impact of school sanitation on students' academic performance</t>
-  </si>
-  <si>
-    <t>Co-supervised a project using automated search extraction to extract and attempted hypotheses using large language models</t>
-  </si>
-  <si>
-    <t>Co-supervised the development of a tool to identify incorrect use of the standard error of measurement instead of the standard deviation in effect size calculations for meta-analyses</t>
   </si>
   <si>
     <t>Workshop on Metacheck</t>
@@ -324,21 +284,6 @@
     <t xml:space="preserve"> Taught multiple regression and power analysis.</t>
   </si>
   <si>
-    <t>Taught introduction to meta-analysis</t>
-  </si>
-  <si>
-    <t>Assisted students during tutorial sessions with course assignments</t>
-  </si>
-  <si>
-    <t>Investigated the effects of two HIIT protocols on VO₂max in highly trained cyclists using physiological assessments, including lactate threshold, VO₂max, and cycling economy testing.</t>
-  </si>
-  <si>
-    <t>Contributed to race analysis and the assessment of swimmers' dry-land performance profiles and propulsive force.</t>
-  </si>
-  <si>
-    <t>Investigated the use of the 1080 Sprint resistance device in swimming to measure power–velocity profiles and estimate drag characteristics in swimmers.</t>
-  </si>
-  <si>
     <t>Funding to develop an R package designed to assist master's students and supervisors in performing automatic checks to enforce best research practices.</t>
   </si>
   <si>
@@ -376,6 +321,75 @@
   </si>
   <si>
     <t>My PhD thesis examined the factors hindering replicability and reproducibility  in sports and exercise science.</t>
+  </si>
+  <si>
+    <t>Lecturer of Advanced Research Methods and Research Ethics</t>
+  </si>
+  <si>
+    <t>Teaching assistant of Advanced Research Methods and Research Ethics</t>
+  </si>
+  <si>
+    <t>Start to Supervise</t>
+  </si>
+  <si>
+    <t>Co-supervised a project creating an automated tool that categorizs repository files based on the file name, index detected variables and their labels, and reconstruct the repository into an established standard.</t>
+  </si>
+  <si>
+    <t>Co-supervised a project using automated search extraction to extract and attempted hypotheses using large language models.</t>
+  </si>
+  <si>
+    <t>Co-supervised a meta-analysis project examining the impact of school sanitation on students' academic performance.</t>
+  </si>
+  <si>
+    <t>Co-supervised the development of a tool to identify incorrect use of the standard error of measurement instead of the standard deviation in effect size calculations for meta-analyses.</t>
+  </si>
+  <si>
+    <t>Taught introduction to meta-analysis.</t>
+  </si>
+  <si>
+    <t>Assisted students during tutorial sessions with course assignments.</t>
+  </si>
+  <si>
+    <t>Taught R Markdown for reproducible reporting and data simulation for statistical analysis.</t>
+  </si>
+  <si>
+    <t>Taught anatomy.</t>
+  </si>
+  <si>
+    <t>Enabling Course for main supervisors.</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Collaborator</t>
+  </si>
+  <si>
+    <t>Technological University Dublin</t>
+  </si>
+  <si>
+    <t>Dublin, Ireland</t>
+  </si>
+  <si>
+    <t>Galway, Ireland</t>
+  </si>
+  <si>
+    <t>Atlantic Technological University Galway</t>
+  </si>
+  <si>
+    <t>Transparency, Technology and AI in peer review Conference</t>
+  </si>
+  <si>
+    <t>I co-organized a one-day conference that brought together different stakeholders to discuss the role of transparency, technology, and AI in peer review (https://meta-eindhoven.github.io/events/).</t>
+  </si>
+  <si>
+    <t>Joe Warne (joe.warne@tudublin.ie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PhD supervisor </t>
+  </si>
+  <si>
+    <t>Jennifer Muprhy (jennifer.murphy@atu.ie)</t>
   </si>
 </sst>
 </file>
@@ -439,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -475,13 +489,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -797,6 +814,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2265E7-B48C-CF42-951E-B253301EB0D2}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="47" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="37.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A70E321-D466-8649-BB94-B1AFF1BE8269}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="35" style="7" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="64.5" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4DFF70-337C-994E-B0CC-B59ADAD82018}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -839,7 +962,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -847,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
@@ -856,7 +979,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -864,7 +987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66DB8938-134D-9E48-B807-361AEFF395A1}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -898,7 +1021,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -907,7 +1030,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -924,7 +1047,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -941,7 +1064,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -958,7 +1081,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -966,14 +1089,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D0B757-8294-AE49-A8E3-ACF99479B5EF}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="5" max="5" width="81.6640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" customWidth="1"/>
+    <col min="5" max="5" width="81.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -989,59 +1113,25 @@
       <c r="D1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="10" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="B2" s="10">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="10" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="10">
-        <v>2017</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="10" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531F101D-2B48-9F46-A53F-FA67ACC31D52}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1079,70 +1169,70 @@
     </row>
     <row r="2" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <v>2024</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1153,21 +1243,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3">
         <v>2024</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>36</v>
@@ -1176,7 +1266,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1191,7 +1281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0F6311-6111-6149-8D98-BE8A9A017CC2}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1220,72 +1310,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2025</v>
+        <v>39</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2026</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3">
         <v>2025</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="6" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3">
         <v>2024</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="6" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2023</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A465BE91-A970-8F4B-854C-C3F13E65FCA4}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1302,7 +1392,7 @@
     <col min="2" max="2" width="17.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="24.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="47.5" style="14" customWidth="1"/>
+    <col min="5" max="5" width="47.5" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -1318,30 +1408,30 @@
       <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
@@ -1353,63 +1443,63 @@
         <v>32</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="12" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5">
         <v>2025</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>95</v>
+        <v>53</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B5" s="5">
         <v>2025</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>96</v>
+        <v>42</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="5">
         <v>2025</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>97</v>
+        <v>44</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5">
         <v>2025</v>
@@ -1420,8 +1510,8 @@
       <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>97</v>
+      <c r="E7" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -1437,8 +1527,8 @@
       <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>80</v>
+      <c r="E8" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
@@ -1455,12 +1545,12 @@
         <v>32</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>34</v>
@@ -1472,24 +1562,24 @@
         <v>36</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B11" s="5">
         <v>2019</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.2">
@@ -1500,7 +1590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C77CB8-88D5-B640-9A7F-46D72B331807}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1527,16 +1617,16 @@
     </row>
     <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3">
         <v>2026</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
@@ -1550,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
